--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1720,6 +1720,958 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126421006</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>525300</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6725055</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126419731</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>525238</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6724951</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126421289</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>525175</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6725002</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Färskare och äldre.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126419660</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>525229</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6724935</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126419646</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>525231</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6724929</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Över ca 0.5kv dm.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126420836</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>525357</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6725062</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126419616</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>525230</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6724936</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126420778</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>525378</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6725045</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -2080,38 +2080,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126419660</v>
+        <v>126419646</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2120,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525229</v>
+        <v>525231</v>
       </c>
       <c r="R14" t="n">
-        <v>6724935</v>
+        <v>6724929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,6 +2175,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>20:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Över ca 0.5kv dm.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,47 +2206,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126419646</v>
+        <v>126419660</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2241,10 +2246,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525231</v>
+        <v>525229</v>
       </c>
       <c r="R15" t="n">
-        <v>6724929</v>
+        <v>6724935</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,11 +2292,6 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>20:16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Över ca 0.5kv dm.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2080,47 +2080,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126419646</v>
+        <v>126419660</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2129,10 +2120,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525231</v>
+        <v>525229</v>
       </c>
       <c r="R14" t="n">
-        <v>6724929</v>
+        <v>6724935</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2175,11 +2166,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>20:16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Över ca 0.5kv dm.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,38 +2192,47 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126419660</v>
+        <v>126419646</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2246,10 +2241,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525229</v>
+        <v>525231</v>
       </c>
       <c r="R15" t="n">
-        <v>6724935</v>
+        <v>6724929</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2292,6 +2287,11 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>20:16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Över ca 0.5kv dm.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2672,6 +2672,693 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126451224</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>525235</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6725126</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126450453</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>525199</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6725063</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126452706</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>525199</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6725060</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126452833</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>525166</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6725043</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126451241</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>525238</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6725124</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126452365</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hjortronbärsmyran, Hjortronbärsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>525207</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6725023</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -1604,7 +1604,7 @@
         <v>126243293</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>126421006</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>126419731</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>126421289</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>126419646</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>126420836</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>126419616</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3359,6 +3359,341 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127314703</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>525142</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6725028</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127313113</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92615</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget N.om, Svarttjärnsberget N.om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>525252</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6725304</v>
+      </c>
+      <c r="S26" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127315781</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>525162</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6725042</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3364,7 +3364,7 @@
         <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127313113</v>
       </c>
       <c r="B26" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3364,7 +3364,7 @@
         <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127313113</v>
       </c>
       <c r="B26" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>127315781</v>
       </c>
       <c r="B27" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3364,7 +3364,7 @@
         <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127313113</v>
       </c>
       <c r="B26" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3364,7 +3364,7 @@
         <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127313113</v>
       </c>
       <c r="B26" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3364,7 +3364,7 @@
         <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127313113</v>
       </c>
       <c r="B26" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3364,7 +3364,7 @@
         <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127313113</v>
       </c>
       <c r="B26" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3364,7 +3364,7 @@
         <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127313113</v>
       </c>
       <c r="B26" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3364,7 +3364,7 @@
         <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127313113</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3694,6 +3694,108 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128692498</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96837</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>525187</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6725005</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Björk, Maria Warg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -3699,7 +3699,7 @@
         <v>128692498</v>
       </c>
       <c r="B28" t="n">
-        <v>96915</v>
+        <v>96924</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3361,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127314703</v>
+        <v>128692498</v>
       </c>
       <c r="B25" t="n">
-        <v>91351</v>
+        <v>96924</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,37 +3372,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525142</v>
+        <v>525187</v>
       </c>
       <c r="R25" t="n">
-        <v>6725028</v>
+        <v>6725005</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3426,22 +3430,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3450,351 +3444,22 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk, Maria Warg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>127313113</v>
-      </c>
-      <c r="B26" t="n">
-        <v>92641</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Svarttjärnsberget N.om, Svarttjärnsberget N.om, Dlr</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>525252</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6725304</v>
-      </c>
-      <c r="S26" t="n">
-        <v>9</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Stora Kopparberg</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>127315781</v>
-      </c>
-      <c r="B27" t="n">
-        <v>5177</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>525162</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6725042</v>
-      </c>
-      <c r="S27" t="n">
-        <v>9</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Stora Kopparberg</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>128692498</v>
-      </c>
-      <c r="B28" t="n">
-        <v>96924</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>53</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Svarttjärnsberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>525187</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6725005</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Stora Kopparberg</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Anton Björk, Maria Warg</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33371-2025 artfynd.xlsx
+++ b/artfynd/A 33371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3361,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128692498</v>
+        <v>127314703</v>
       </c>
       <c r="B25" t="n">
-        <v>96924</v>
+        <v>91351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,41 +3372,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525187</v>
+        <v>525142</v>
       </c>
       <c r="R25" t="n">
-        <v>6725005</v>
+        <v>6725028</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3430,12 +3426,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3444,22 +3450,351 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127313113</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92641</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget N.om, Svarttjärnsberget N.om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>525252</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6725304</v>
+      </c>
+      <c r="S26" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127315781</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>525162</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6725042</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128692498</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96924</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>525187</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6725005</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Anton Björk, Maria Warg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
